--- a/server/files/631-12.xlsx
+++ b/server/files/631-12.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Пользователь\Desktop\Расписание ОСЕНЬ 25_26\Вариант_2\Расписание занятий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Андрей Майоров\Documents\Webwork\schedule-viewer\server\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96336123-A6DF-4552-A8AC-2B259F241973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="5595"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -4210,7 +4211,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d"/>
   </numFmts>
@@ -4602,56 +4603,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4926,19 +4878,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -4975,7 +4927,7 @@
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
@@ -5012,7 +4964,7 @@
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
     </row>
-    <row r="3" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5051,7 +5003,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:31" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5140,7 +5092,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
@@ -5187,7 +5139,7 @@
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>25</v>
       </c>
@@ -5278,7 +5230,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A7" s="50"/>
       <c r="B7" s="7" t="s">
         <v>16</v>
@@ -5357,7 +5309,7 @@
       <c r="AD7" s="12"/>
       <c r="AE7" s="12"/>
     </row>
-    <row r="8" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A8" s="50"/>
       <c r="B8" s="7" t="s">
         <v>17</v>
@@ -5436,7 +5388,7 @@
       <c r="AD8" s="12"/>
       <c r="AE8" s="12"/>
     </row>
-    <row r="9" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
       <c r="B9" s="7" t="s">
         <v>18</v>
@@ -5515,7 +5467,7 @@
       <c r="AD9" s="12"/>
       <c r="AE9" s="12"/>
     </row>
-    <row r="10" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A10" s="50"/>
       <c r="B10" s="7" t="s">
         <v>19</v>
@@ -5594,7 +5546,7 @@
       <c r="AD10" s="12"/>
       <c r="AE10" s="12"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>26</v>
       </c>
@@ -5685,7 +5637,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A12" s="50"/>
       <c r="B12" s="7" t="s">
         <v>16</v>
@@ -5764,7 +5716,7 @@
       <c r="AD12" s="12"/>
       <c r="AE12" s="12"/>
     </row>
-    <row r="13" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A13" s="50"/>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -5843,7 +5795,7 @@
       <c r="AD13" s="12"/>
       <c r="AE13" s="12"/>
     </row>
-    <row r="14" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A14" s="50"/>
       <c r="B14" s="7" t="s">
         <v>18</v>
@@ -5922,7 +5874,7 @@
       <c r="AD14" s="12"/>
       <c r="AE14" s="12"/>
     </row>
-    <row r="15" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A15" s="50"/>
       <c r="B15" s="7" t="s">
         <v>19</v>
@@ -6001,7 +5953,7 @@
       <c r="AD15" s="12"/>
       <c r="AE15" s="12"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
         <v>27</v>
       </c>
@@ -6092,7 +6044,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A17" s="50"/>
       <c r="B17" s="7" t="s">
         <v>16</v>
@@ -6171,7 +6123,7 @@
       <c r="AD17" s="12"/>
       <c r="AE17" s="12"/>
     </row>
-    <row r="18" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A18" s="50"/>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -6250,7 +6202,7 @@
       <c r="AD18" s="12"/>
       <c r="AE18" s="12"/>
     </row>
-    <row r="19" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A19" s="50"/>
       <c r="B19" s="7" t="s">
         <v>18</v>
@@ -6329,7 +6281,7 @@
       <c r="AD19" s="12"/>
       <c r="AE19" s="12"/>
     </row>
-    <row r="20" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A20" s="50"/>
       <c r="B20" s="7" t="s">
         <v>19</v>
@@ -6408,7 +6360,7 @@
       <c r="AD20" s="12"/>
       <c r="AE20" s="12"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="50" t="s">
         <v>28</v>
       </c>
@@ -6499,7 +6451,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A22" s="50"/>
       <c r="B22" s="7" t="s">
         <v>16</v>
@@ -6578,7 +6530,7 @@
       <c r="AD22" s="12"/>
       <c r="AE22" s="12"/>
     </row>
-    <row r="23" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A23" s="50"/>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -6657,7 +6609,7 @@
       <c r="AD23" s="12"/>
       <c r="AE23" s="12"/>
     </row>
-    <row r="24" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A24" s="50"/>
       <c r="B24" s="7" t="s">
         <v>18</v>
@@ -6736,7 +6688,7 @@
       <c r="AD24" s="12"/>
       <c r="AE24" s="12"/>
     </row>
-    <row r="25" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A25" s="50"/>
       <c r="B25" s="7" t="s">
         <v>19</v>
@@ -6815,7 +6767,7 @@
       <c r="AD25" s="12"/>
       <c r="AE25" s="12"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" s="50" t="s">
         <v>29</v>
       </c>
@@ -6906,7 +6858,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A27" s="50"/>
       <c r="B27" s="7" t="s">
         <v>16</v>
@@ -6985,7 +6937,7 @@
       <c r="AD27" s="12"/>
       <c r="AE27" s="12"/>
     </row>
-    <row r="28" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A28" s="50"/>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -7064,7 +7016,7 @@
       <c r="AD28" s="12"/>
       <c r="AE28" s="12"/>
     </row>
-    <row r="29" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A29" s="50"/>
       <c r="B29" s="7" t="s">
         <v>18</v>
@@ -7143,7 +7095,7 @@
       <c r="AD29" s="12"/>
       <c r="AE29" s="12"/>
     </row>
-    <row r="30" spans="1:31" ht="57" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="56.4" x14ac:dyDescent="0.3">
       <c r="A30" s="50"/>
       <c r="B30" s="7" t="s">
         <v>19</v>
@@ -7222,7 +7174,7 @@
       <c r="AD30" s="12"/>
       <c r="AE30" s="12"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" s="50" t="s">
         <v>30</v>
       </c>
@@ -7313,7 +7265,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="72" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="70.8" x14ac:dyDescent="0.3">
       <c r="A32" s="50"/>
       <c r="B32" s="7" t="s">
         <v>16</v>
@@ -7392,7 +7344,7 @@
       <c r="AD32" s="12"/>
       <c r="AE32" s="12"/>
     </row>
-    <row r="33" spans="1:31" ht="72" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="70.8" x14ac:dyDescent="0.3">
       <c r="A33" s="50"/>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -7471,7 +7423,7 @@
       <c r="AD33" s="12"/>
       <c r="AE33" s="12"/>
     </row>
-    <row r="34" spans="1:31" ht="72" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="70.8" x14ac:dyDescent="0.3">
       <c r="A34" s="51"/>
       <c r="B34" s="14" t="s">
         <v>18</v>
@@ -7550,7 +7502,7 @@
       <c r="AD34" s="17"/>
       <c r="AE34" s="17"/>
     </row>
-    <row r="36" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="49" t="s">
         <v>99</v>
       </c>
@@ -7601,7 +7553,7 @@
       <c r="AD36" s="46"/>
       <c r="AE36" s="47"/>
     </row>
-    <row r="37" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="49"/>
       <c r="B37" s="46"/>
       <c r="C37" s="46"/>
@@ -7636,7 +7588,7 @@
       <c r="AD37" s="46"/>
       <c r="AE37" s="47"/>
     </row>
-    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="49"/>
       <c r="B38" s="46"/>
       <c r="C38" s="46"/>
@@ -7675,7 +7627,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20" t="s">
         <v>100</v>
       </c>
@@ -7722,7 +7674,7 @@
       <c r="AD39" s="21"/>
       <c r="AE39" s="22"/>
     </row>
-    <row r="40" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20" t="s">
         <v>101</v>
       </c>
@@ -7767,7 +7719,7 @@
       <c r="AD40" s="21"/>
       <c r="AE40" s="22"/>
     </row>
-    <row r="41" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
         <v>102</v>
       </c>
@@ -7814,7 +7766,7 @@
       <c r="AD41" s="21"/>
       <c r="AE41" s="22"/>
     </row>
-    <row r="42" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
         <v>102</v>
       </c>
@@ -7861,7 +7813,7 @@
       <c r="AD42" s="21"/>
       <c r="AE42" s="22"/>
     </row>
-    <row r="43" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
         <v>103</v>
       </c>
@@ -7908,7 +7860,7 @@
       <c r="AD43" s="21"/>
       <c r="AE43" s="22"/>
     </row>
-    <row r="44" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20" t="s">
         <v>104</v>
       </c>
@@ -7955,7 +7907,7 @@
       <c r="AD44" s="21"/>
       <c r="AE44" s="22"/>
     </row>
-    <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20" t="s">
         <v>105</v>
       </c>
@@ -8002,7 +7954,7 @@
       <c r="AD45" s="21"/>
       <c r="AE45" s="22"/>
     </row>
-    <row r="46" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>106</v>
       </c>
@@ -8049,7 +8001,7 @@
       <c r="AD46" s="21"/>
       <c r="AE46" s="22"/>
     </row>
-    <row r="47" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20" t="s">
         <v>107</v>
       </c>
@@ -8094,7 +8046,7 @@
       <c r="AD47" s="21"/>
       <c r="AE47" s="22"/>
     </row>
-    <row r="48" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20" t="s">
         <v>108</v>
       </c>
@@ -8139,7 +8091,7 @@
       <c r="AD48" s="21"/>
       <c r="AE48" s="22"/>
     </row>
-    <row r="49" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
         <v>109</v>
       </c>
@@ -8186,7 +8138,7 @@
       <c r="AD49" s="21"/>
       <c r="AE49" s="22"/>
     </row>
-    <row r="51" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="s">
         <v>160</v>
       </c>
@@ -8227,7 +8179,7 @@
       <c r="AD51" s="25"/>
       <c r="AE51" s="25"/>
     </row>
-    <row r="52" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="26" t="s">
         <v>161</v>
       </c>
@@ -8268,7 +8220,7 @@
       <c r="AD52" s="25"/>
       <c r="AE52" s="25"/>
     </row>
-    <row r="53" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>162</v>
       </c>
@@ -8309,7 +8261,7 @@
       <c r="AD53" s="25"/>
       <c r="AE53" s="25"/>
     </row>
-    <row r="54" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="26" t="s">
         <v>163</v>
       </c>
@@ -8350,7 +8302,7 @@
       <c r="AD54" s="25"/>
       <c r="AE54" s="25"/>
     </row>
-    <row r="55" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="26" t="s">
         <v>164</v>
       </c>
@@ -8389,7 +8341,7 @@
       <c r="AD55" s="25"/>
       <c r="AE55" s="25"/>
     </row>
-    <row r="56" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
         <v>165</v>
       </c>
@@ -8428,7 +8380,7 @@
       <c r="AD56" s="25"/>
       <c r="AE56" s="25"/>
     </row>
-    <row r="57" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>166</v>
       </c>
@@ -8467,7 +8419,7 @@
       <c r="AD57" s="25"/>
       <c r="AE57" s="25"/>
     </row>
-    <row r="58" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="26" t="s">
         <v>167</v>
       </c>
@@ -8506,7 +8458,7 @@
       <c r="AD58" s="25"/>
       <c r="AE58" s="25"/>
     </row>
-    <row r="59" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
         <v>168</v>
       </c>
@@ -8545,7 +8497,7 @@
       <c r="AD59" s="25"/>
       <c r="AE59" s="25"/>
     </row>
-    <row r="60" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="26" t="s">
         <v>169</v>
       </c>
@@ -8582,7 +8534,7 @@
       <c r="AD60" s="25"/>
       <c r="AE60" s="25"/>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A61" s="25"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -8615,7 +8567,7 @@
       <c r="AD61" s="25"/>
       <c r="AE61" s="25"/>
     </row>
-    <row r="62" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="25"/>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
@@ -8650,7 +8602,7 @@
       <c r="AD62" s="25"/>
       <c r="AE62" s="25"/>
     </row>
-    <row r="63" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="W63" s="28" t="s">
         <v>192</v>
       </c>
@@ -8660,7 +8612,7 @@
       <c r="AA63" s="28"/>
       <c r="AB63" s="28"/>
     </row>
-    <row r="64" spans="1:31" ht="18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="W64" s="28"/>
       <c r="X64" s="28"/>
       <c r="Y64" s="28"/>
@@ -8668,7 +8620,7 @@
       <c r="AA64" s="28"/>
       <c r="AB64" s="28"/>
     </row>
-    <row r="65" spans="23:28" ht="18" x14ac:dyDescent="0.3">
+    <row r="65" spans="23:28" ht="18" x14ac:dyDescent="0.35">
       <c r="W65" s="28"/>
       <c r="X65" s="28"/>
       <c r="Y65" s="28"/>
@@ -8676,7 +8628,7 @@
       <c r="AA65" s="28"/>
       <c r="AB65" s="28"/>
     </row>
-    <row r="66" spans="23:28" ht="18" x14ac:dyDescent="0.3">
+    <row r="66" spans="23:28" ht="18" x14ac:dyDescent="0.35">
       <c r="W66" s="28"/>
       <c r="X66" s="28"/>
       <c r="Y66" s="28"/>
